--- a/Configs/GameConfig/Datas/result_schema.xlsx
+++ b/Configs/GameConfig/Datas/result_schema.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R47c4ec30dc004a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52906c75cb154ba3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,12 +334,8 @@
       <x:c r="B1" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" t="str">
-        <x:v>field</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>typeDesc</x:v>
-      </x:c>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -348,12 +344,8 @@
       <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>string</x:v>
-      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -368,170 +360,114 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>字段(主键)</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>类型描述</x:v>
-      </x:c>
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>isWin</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>boolean</x:v>
-      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>star</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>gold</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>battleDuration</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>milliseconds</x:v>
-      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>round</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>playerTargetHealth</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>opponentTargetHealth</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>weaponFragments</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>array</x:v>
-      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C13" t="str">
-        <x:v>killCount</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>bossKillCount</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C15" t="str">
-        <x:v>endlessRound</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>number</x:v>
-      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>gameMode</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>normal|endless</x:v>
-      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17"/>
       <x:c r="B17" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>resultState</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>WIN|LOSE</x:v>
-      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
